--- a/getpower.xlsx
+++ b/getpower.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stanley_hu\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stanley_hu\claude-test\lunchbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B36DE65-882D-429B-BFD5-9563B8BF7BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D24D50A-BD43-4675-ABCB-5022AFE00216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00A76E43-0CB4-48C0-887E-58B32B8B3C55}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
   <si>
     <r>
       <rPr>
@@ -73,19 +73,6 @@
         <family val="1"/>
         <charset val="136"/>
       </rPr>
-      <t>單價</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
       <t>總價</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -148,10 +135,51 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>韓式泡菜豬肉片</t>
-  </si>
-  <si>
     <t>南加州火烤雞胸</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒜泥醬豬肉片</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>樹子汁蒸鱸魚</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>單價</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔香火烤雞胸</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>南加州烤雞腿</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>單</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>點主菜</t>
+    </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -159,7 +187,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -218,25 +246,50 @@
     </font>
     <font>
       <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft JhengHei"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -255,12 +308,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -276,7 +323,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -307,19 +354,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -327,6 +365,21 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -662,7 +715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23CFCC0E-2C5E-419D-B82E-019972F8D5A9}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="21"/>
   <cols>
     <col min="1" max="1" width="23.109375" style="2" bestFit="1" customWidth="1"/>
@@ -681,28 +734,28 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" s="5"/>
-      <c r="C2" s="13">
+      <c r="C2" s="10">
         <v>140</v>
       </c>
       <c r="D2" s="5"/>
@@ -710,7 +763,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="6">
         <v>125</v>
@@ -720,7 +773,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5">
@@ -731,7 +784,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="6">
         <v>125</v>
@@ -741,7 +794,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
@@ -752,7 +805,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
@@ -763,7 +816,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="6">
         <v>160</v>
@@ -772,7 +825,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" s="6">
         <v>110</v>
@@ -781,16 +834,16 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="14">
+        <v>14</v>
+      </c>
+      <c r="C10" s="11">
         <v>130</v>
       </c>
       <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" s="6">
         <v>220</v>
@@ -798,67 +851,130 @@
       <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="12">
+        <v>125</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="7"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" ht="21.6">
+      <c r="A15" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="6">
+        <v>80</v>
+      </c>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="6">
+        <v>70</v>
+      </c>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="1:4" ht="22.2">
+      <c r="A18" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="6">
+        <v>160</v>
+      </c>
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="1:4" ht="22.2">
+      <c r="A19" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="6">
+        <v>65</v>
+      </c>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="1:4" ht="22.2">
+      <c r="A20" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="6">
+        <v>65</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:4" ht="22.2">
+      <c r="A21" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="6">
+        <v>65</v>
+      </c>
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="1:4" ht="22.2">
+      <c r="A22" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="6">
+        <v>75</v>
+      </c>
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" spans="1:4" ht="24.6" customHeight="1">
+      <c r="A23" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="6">
+        <v>65</v>
+      </c>
+      <c r="D23" s="5"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="11">
-        <v>130</v>
-      </c>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="15">
-        <v>125</v>
-      </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="7"/>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="7"/>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="7"/>
-      <c r="D17" s="5"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="D18" s="5"/>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="D19" s="5"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="D21" s="5"/>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="D22" s="5"/>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="D23" s="5"/>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="C24" s="6">
+        <v>65</v>
+      </c>
       <c r="D24" s="5"/>
     </row>
     <row r="25" spans="1:4">
+      <c r="A25" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="6">
+        <v>100</v>
+      </c>
       <c r="D25" s="5"/>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" ht="22.2">
+      <c r="A26" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="6">
+        <v>50</v>
+      </c>
       <c r="D26" s="5"/>
     </row>
     <row r="27" spans="1:4">
@@ -869,6 +985,24 @@
     </row>
     <row r="29" spans="1:4">
       <c r="D29" s="5"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="D30" s="5"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="D31" s="5"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="D32" s="5"/>
+    </row>
+    <row r="33" spans="4:4">
+      <c r="D33" s="5"/>
+    </row>
+    <row r="34" spans="4:4">
+      <c r="D34" s="5"/>
+    </row>
+    <row r="35" spans="4:4">
+      <c r="D35" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
